--- a/data/trans_orig/IP07A16-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07A16-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de ayudarse entre los amigos en 2007 (tasa de respuesta: 99,2%)</t>
+          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el adulto en 2007 (tasa de respuesta: 99,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22417</t>
+          <t>22632</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35106</t>
+          <t>35837</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31604</t>
+          <t>31225</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46186</t>
+          <t>46137</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57657</t>
+          <t>58756</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76589</t>
+          <t>77641</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>53,61%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25441</t>
+          <t>24621</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38256</t>
+          <t>37890</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,82 +860,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>38,46%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>59,19%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>35825</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>28960</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>43569</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>44,33%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>35,84%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>53,91%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>67462</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>57561</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>76830</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>46,58%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>39,74%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>59,76%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>35825</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>28273</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>43243</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>44,33%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>34,98%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>53,51%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>67462</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>59111</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>77917</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>46,58%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>40,81%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,05%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7798</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10761</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>5727</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16213</t>
+          <t>15925</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47626</t>
+          <t>48946</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63700</t>
+          <t>64621</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36006</t>
+          <t>35355</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51690</t>
+          <t>50632</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87718</t>
+          <t>90264</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111295</t>
+          <t>112130</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>55,17%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29475</t>
+          <t>29118</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44081</t>
+          <t>44644</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39510</t>
+          <t>39658</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55043</t>
+          <t>54496</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72432</t>
+          <t>72277</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>95003</t>
+          <t>93774</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,14%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>6456</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16330</t>
+          <t>15849</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13311</t>
+          <t>13629</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13507</t>
+          <t>13312</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26998</t>
+          <t>26482</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>3686</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28253</t>
+          <t>28186</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39951</t>
+          <t>40304</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32475</t>
+          <t>31737</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45107</t>
+          <t>44184</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63267</t>
+          <t>63961</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80668</t>
+          <t>80931</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,87%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14402</t>
+          <t>14196</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25327</t>
+          <t>25634</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16037</t>
+          <t>15552</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27519</t>
+          <t>27119</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32844</t>
+          <t>33418</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49418</t>
+          <t>48582</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,34%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9763</t>
+          <t>9692</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>2786</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>10228</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16562</t>
+          <t>16957</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2425</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27899</t>
+          <t>27944</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43746</t>
+          <t>43683</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36256</t>
+          <t>36125</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52762</t>
+          <t>52375</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>68361</t>
+          <t>69141</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90371</t>
+          <t>90992</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>48,14%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29953</t>
+          <t>29899</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45817</t>
+          <t>45543</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33484</t>
+          <t>34488</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49946</t>
+          <t>50299</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>68826</t>
+          <t>67945</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>91241</t>
+          <t>91092</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,19%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10919</t>
+          <t>11012</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22969</t>
+          <t>22933</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7414</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17697</t>
+          <t>18160</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21419</t>
+          <t>20306</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>38179</t>
+          <t>37055</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>141217</t>
+          <t>141130</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>170193</t>
+          <t>170443</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>151318</t>
+          <t>150567</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>179244</t>
+          <t>180296</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>298967</t>
+          <t>299590</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>342634</t>
+          <t>341172</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,4%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>111637</t>
+          <t>111218</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>139724</t>
+          <t>139471</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>131597</t>
+          <t>129794</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>159695</t>
+          <t>159506</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>248607</t>
+          <t>250093</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>292369</t>
+          <t>292935</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,13%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>27038</t>
+          <t>27152</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>46715</t>
+          <t>45400</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>24157</t>
+          <t>24018</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>42223</t>
+          <t>40815</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>56279</t>
+          <t>56509</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>80962</t>
+          <t>81764</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2446</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>7208</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de ayudarse entre los amigos en 2012 (tasa de respuesta: 97,81%)</t>
+          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el adulto en 2012 (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30032</t>
+          <t>31010</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44821</t>
+          <t>44503</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29424</t>
+          <t>28763</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43715</t>
+          <t>43325</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64360</t>
+          <t>65143</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83373</t>
+          <t>83916</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,98%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15482</t>
+          <t>15593</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29234</t>
+          <t>28122</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21186</t>
+          <t>21255</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35683</t>
+          <t>35584</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41237</t>
+          <t>40734</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59008</t>
+          <t>59389</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>43,16%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>731</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7380</t>
+          <t>7684</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>6081</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16066</t>
+          <t>15846</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3547</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>659</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6840</t>
+          <t>6347</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6212</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41483</t>
+          <t>41619</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57067</t>
+          <t>56840</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43177</t>
+          <t>44313</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59577</t>
+          <t>59945</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90972</t>
+          <t>90545</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>112773</t>
+          <t>112594</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,74%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34526</t>
+          <t>35395</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50386</t>
+          <t>50672</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28299</t>
+          <t>28553</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43581</t>
+          <t>43833</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67650</t>
+          <t>68113</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>88962</t>
+          <t>89471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,89%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9538</t>
+          <t>9512</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12777</t>
+          <t>13157</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>8189</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19389</t>
+          <t>19211</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24802</t>
+          <t>24782</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37222</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36567</t>
+          <t>36519</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49999</t>
+          <t>49544</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64851</t>
+          <t>65544</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83137</t>
+          <t>84423</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>62,38%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21372</t>
+          <t>21601</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34457</t>
+          <t>34463</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13860</t>
+          <t>13974</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25495</t>
+          <t>25354</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38360</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57358</t>
+          <t>55631</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>41,11%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2527</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9848</t>
+          <t>9614</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1688</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8800</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5896</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16209</t>
+          <t>15870</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>4031</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6366</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7456</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33892</t>
+          <t>35409</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51134</t>
+          <t>52065</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35896</t>
+          <t>35637</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50983</t>
+          <t>51451</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>75266</t>
+          <t>75240</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>97825</t>
+          <t>98809</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,57%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31674</t>
+          <t>30710</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47513</t>
+          <t>47660</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31265</t>
+          <t>30749</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>46433</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>66035</t>
+          <t>64922</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>88193</t>
+          <t>88227</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,83%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3677</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13087</t>
+          <t>13307</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14026</t>
+          <t>14019</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10330</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23834</t>
+          <t>24064</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>6766</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>947</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8075</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>145184</t>
+          <t>145896</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>174149</t>
+          <t>175147</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>161335</t>
+          <t>161566</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>190649</t>
+          <t>190103</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>315991</t>
+          <t>314271</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>358765</t>
+          <t>359237</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>55,07%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>116830</t>
+          <t>117363</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>146290</t>
+          <t>145733</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>107860</t>
+          <t>107595</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>135649</t>
+          <t>135452</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>233344</t>
+          <t>233393</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>274072</t>
+          <t>274732</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,11%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>13996</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>28708</t>
+          <t>28683</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>20542</t>
+          <t>20927</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>37259</t>
+          <t>37183</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>39665</t>
+          <t>38062</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>61503</t>
+          <t>60435</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>1686</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9650</t>
+          <t>9368</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9171</t>
+          <t>8862</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>14514</t>
+          <t>15202</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8832</t>
+          <t>8708</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10680</t>
+          <t>10721</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de ayudarse entre los amigos en 2016 (tasa de respuesta: 98,43%)</t>
+          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el adulto en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28838</t>
+          <t>29092</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43422</t>
+          <t>43134</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31485</t>
+          <t>31664</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46821</t>
+          <t>47621</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64034</t>
+          <t>66262</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85936</t>
+          <t>85990</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,52%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>20367</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33438</t>
+          <t>34051</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22804</t>
+          <t>21984</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37494</t>
+          <t>36959</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46445</t>
+          <t>46568</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65598</t>
+          <t>65683</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,47%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3111</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12514</t>
+          <t>11716</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,82 +8257,82 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>16,54%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>4455</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>9495</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>12,9%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>11063</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>6346</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>18232</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>7,66%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>4,39%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>17,66%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4455</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1551</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9308</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>12,64%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>11063</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>6295</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>18442</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>7,66%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6269</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>5832</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52361</t>
+          <t>53200</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69137</t>
+          <t>69138</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45766</t>
+          <t>47044</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63359</t>
+          <t>63487</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>104221</t>
+          <t>104648</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126838</t>
+          <t>126965</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>59,84%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25374</t>
+          <t>25839</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40671</t>
+          <t>40649</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31769</t>
+          <t>32098</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48535</t>
+          <t>48560</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>62767</t>
+          <t>63190</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>84808</t>
+          <t>85688</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,38%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15775</t>
+          <t>15301</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>5515</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15045</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13772</t>
+          <t>13254</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26728</t>
+          <t>26458</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>692</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -9190,7 +9190,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>3944</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35648</t>
+          <t>36023</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48873</t>
+          <t>49109</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40265</t>
+          <t>39928</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55184</t>
+          <t>55382</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>80345</t>
+          <t>80208</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>100904</t>
+          <t>100031</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,14%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17018</t>
+          <t>16999</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29397</t>
+          <t>29627</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17490</t>
+          <t>17568</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31715</t>
+          <t>32207</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37932</t>
+          <t>37988</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55889</t>
+          <t>56371</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,83%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11008</t>
+          <t>11055</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1555</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5686</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>16776</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53139</t>
+          <t>52674</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70819</t>
+          <t>70346</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50893</t>
+          <t>50351</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67498</t>
+          <t>66885</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>109374</t>
+          <t>109558</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>133351</t>
+          <t>133827</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>64,24%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25578</t>
+          <t>25666</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>42214</t>
+          <t>42436</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25223</t>
+          <t>25574</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41345</t>
+          <t>41244</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>54896</t>
+          <t>55331</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>77879</t>
+          <t>78406</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,64%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16395</t>
+          <t>15671</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13089</t>
+          <t>12597</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12207</t>
+          <t>11355</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25404</t>
+          <t>25366</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>726</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>6726</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>3980</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>186121</t>
+          <t>187710</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>217365</t>
+          <t>216261</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>186005</t>
+          <t>185946</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>218520</t>
+          <t>217062</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>380451</t>
+          <t>382305</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>424121</t>
+          <t>425804</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,64%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>100722</t>
+          <t>100133</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>129039</t>
+          <t>129206</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>111992</t>
+          <t>111627</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>142218</t>
+          <t>142207</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>221450</t>
+          <t>220659</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>262250</t>
+          <t>263300</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,88%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>23663</t>
+          <t>23680</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>41923</t>
+          <t>42420</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18224</t>
+          <t>18563</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>34803</t>
+          <t>35150</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>46788</t>
+          <t>47572</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>70583</t>
+          <t>72876</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>15434</t>
+          <t>14972</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>4667</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
